--- a/data/NCC_Compiled_Tenure_Data_Sources/Blue Carbon - ATL Tenure Data.xlsx
+++ b/data/NCC_Compiled_Tenure_Data_Sources/Blue Carbon - ATL Tenure Data.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://itncc-my.sharepoint.com/personal/andrea_hebb_natureconservancy_ca/Documents/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mcgill.sharepoint.com/sites/QuantitativeBiodiversityLab_Group/Shared Documents/Blitz the Gap/ten_layers/land_tenure_layer/cloud_native_canada_land_tenure/data/NCC_Compiled_Tenure_Data_Sources/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3AE0910C-6672-43C7-B94F-8A0A974B8067}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="8_{3AE0910C-6672-43C7-B94F-8A0A974B8067}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AE367833-0CFC-45FC-ADEF-14DFC366DB1E}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13872" xr2:uid="{F393B842-E587-4FFF-9905-2C3ECACA8BC3}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{F393B842-E587-4FFF-9905-2C3ECACA8BC3}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -369,7 +369,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -382,16 +382,11 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -728,16 +723,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{15A13B20-ED50-435C-A8CE-C4AE442B7858}">
   <dimension ref="A1:E28"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="64.20703125" customWidth="1"/>
-    <col min="2" max="2" width="7.62890625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="35.83984375" customWidth="1"/>
-    <col min="4" max="4" width="39.83984375" customWidth="1"/>
-    <col min="5" max="5" width="96.41796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="64.1796875" customWidth="1"/>
+    <col min="2" max="2" width="7.6328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="35.81640625" customWidth="1"/>
+    <col min="4" max="4" width="39.81640625" customWidth="1"/>
+    <col min="5" max="5" width="96.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -754,7 +749,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
         <v>7</v>
       </c>
@@ -771,7 +766,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
         <v>11</v>
       </c>
@@ -788,7 +783,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
         <v>15</v>
       </c>
@@ -803,7 +798,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" s="4" t="s">
         <v>17</v>
       </c>
@@ -818,7 +813,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
         <v>19</v>
       </c>
@@ -833,7 +828,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
         <v>21</v>
       </c>
@@ -848,7 +843,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
         <v>23</v>
       </c>
@@ -863,7 +858,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
         <v>25</v>
       </c>
@@ -880,97 +875,97 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:5" s="10" customFormat="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" s="8" t="s">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A10" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="B10" s="8" t="s">
+      <c r="B10" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="C10" s="8" t="s">
+      <c r="C10" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="D10" s="8"/>
-      <c r="E10" s="9" t="s">
+      <c r="D10" s="4"/>
+      <c r="E10" s="7" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="11" spans="1:5" s="10" customFormat="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A11" s="8" t="s">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A11" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="B11" s="8" t="s">
+      <c r="B11" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="C11" s="8" t="s">
+      <c r="C11" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="D11" s="8"/>
-      <c r="E11" s="9" t="s">
+      <c r="D11" s="4"/>
+      <c r="E11" s="6" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="12" spans="1:5" s="10" customFormat="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A12" s="8" t="s">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A12" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="B12" s="8" t="s">
+      <c r="B12" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="C12" s="8" t="s">
+      <c r="C12" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="D12" s="8"/>
-      <c r="E12" s="11" t="s">
+      <c r="D12" s="4"/>
+      <c r="E12" s="8" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="13" spans="1:5" s="10" customFormat="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A13" s="8" t="s">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A13" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="B13" s="8" t="s">
+      <c r="B13" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="C13" s="8" t="s">
+      <c r="C13" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="D13" s="8"/>
-      <c r="E13" s="9" t="s">
+      <c r="D13" s="4"/>
+      <c r="E13" s="7" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="14" spans="1:5" s="10" customFormat="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A14" s="8" t="s">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A14" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="B14" s="8" t="s">
+      <c r="B14" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="C14" s="8" t="s">
+      <c r="C14" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="D14" s="8"/>
-      <c r="E14" s="9" t="s">
+      <c r="D14" s="4"/>
+      <c r="E14" s="6" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="15" spans="1:5" s="10" customFormat="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A15" s="8" t="s">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A15" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="B15" s="8" t="s">
+      <c r="B15" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="C15" s="8" t="s">
+      <c r="C15" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="D15" s="8"/>
-      <c r="E15" s="9" t="s">
+      <c r="D15" s="4"/>
+      <c r="E15" s="6" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A16" s="3" t="s">
         <v>41</v>
       </c>
@@ -987,7 +982,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A17" s="3" t="s">
         <v>42</v>
       </c>
@@ -1000,7 +995,7 @@
       <c r="D17" s="5"/>
       <c r="E17" s="6"/>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A18" s="3" t="s">
         <v>44</v>
       </c>
@@ -1017,7 +1012,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A19" s="3" t="s">
         <v>48</v>
       </c>
@@ -1034,140 +1029,140 @@
         <v>47</v>
       </c>
     </row>
-    <row r="20" spans="1:5" s="10" customFormat="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A20" s="11" t="s">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A20" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="B20" s="12" t="s">
+      <c r="B20" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="C20" s="12" t="s">
+      <c r="C20" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="D20" s="13" t="s">
+      <c r="D20" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="E20" s="14"/>
-    </row>
-    <row r="21" spans="1:5" s="10" customFormat="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A21" s="11" t="s">
+      <c r="E20" s="11"/>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A21" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="B21" s="12" t="s">
+      <c r="B21" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="C21" s="12" t="s">
+      <c r="C21" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="D21" s="13" t="s">
+      <c r="D21" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="E21" s="14"/>
-    </row>
-    <row r="22" spans="1:5" s="10" customFormat="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A22" s="15" t="s">
+      <c r="E21" s="11"/>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A22" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="B22" s="15" t="s">
+      <c r="B22" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="C22" s="15" t="s">
+      <c r="C22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D22" s="16" t="s">
+      <c r="D22" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="E22" s="9"/>
-    </row>
-    <row r="23" spans="1:5" s="10" customFormat="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A23" s="8" t="s">
+      <c r="E22" s="6"/>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A23" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="B23" s="8" t="s">
+      <c r="B23" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="C23" s="8" t="s">
+      <c r="C23" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="D23" s="8"/>
-      <c r="E23" s="11" t="s">
+      <c r="D23" s="4"/>
+      <c r="E23" s="8" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="24" spans="1:5" s="10" customFormat="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A24" s="8" t="s">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A24" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="B24" s="8" t="s">
+      <c r="B24" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="C24" s="8" t="s">
+      <c r="C24" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="D24" s="8"/>
-      <c r="E24" s="11" t="s">
+      <c r="D24" s="4"/>
+      <c r="E24" s="8" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="25" spans="1:5" s="10" customFormat="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A25" s="8" t="s">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A25" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="B25" s="8" t="s">
+      <c r="B25" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="C25" s="8" t="s">
+      <c r="C25" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="D25" s="8"/>
-      <c r="E25" s="11" t="s">
+      <c r="D25" s="4"/>
+      <c r="E25" s="8" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="26" spans="1:5" s="10" customFormat="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A26" s="15" t="s">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A26" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="B26" s="15" t="s">
+      <c r="B26" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C26" s="15" t="s">
+      <c r="C26" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D26" s="16" t="s">
+      <c r="D26" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="E26" s="11" t="s">
+      <c r="E26" s="8" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="27" spans="1:5" s="10" customFormat="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A27" s="8" t="s">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A27" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="B27" s="8" t="s">
+      <c r="B27" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C27" s="8" t="s">
+      <c r="C27" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="D27" s="8"/>
-      <c r="E27" s="11" t="s">
+      <c r="D27" s="4"/>
+      <c r="E27" s="8" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="28" spans="1:5" s="10" customFormat="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A28" s="17" t="s">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A28" s="12" t="s">
         <v>67</v>
       </c>
-      <c r="B28" s="17" t="s">
+      <c r="B28" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="C28" s="17" t="s">
+      <c r="C28" s="12" t="s">
         <v>68</v>
       </c>
-      <c r="D28" s="17"/>
-      <c r="E28" s="11" t="s">
+      <c r="D28" s="12"/>
+      <c r="E28" s="8" t="s">
         <v>69</v>
       </c>
     </row>
@@ -1193,14 +1188,36 @@
     <hyperlink ref="E26" r:id="rId18" xr:uid="{79C9DC5C-E073-4883-B863-30A17380C2DE}"/>
     <hyperlink ref="E27" r:id="rId19" xr:uid="{8A95CBE2-7F0E-47E2-8E9D-74FA5DCD13EC}"/>
     <hyperlink ref="E28" r:id="rId20" xr:uid="{E64B1A49-4482-4F1A-916F-CA25AA0C913A}"/>
+    <hyperlink ref="E10" r:id="rId21" xr:uid="{E60AB75E-85E7-4251-AA75-0793F74CA729}"/>
+    <hyperlink ref="E13" r:id="rId22" xr:uid="{0B5B6698-122E-4CD9-8F96-DFF150F273DB}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010023058B3D7F88F54B8F614B4819A3D2C3" ma:contentTypeVersion="20" ma:contentTypeDescription="Crée un document." ma:contentTypeScope="" ma:versionID="9c95790c7176aca22ec34ce72732b57f">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="c44aea68-f73b-45d5-b042-7c498dcb23dc" xmlns:ns3="634edf18-62ba-46f2-a3a7-063d8fb172d8" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="25574f8a6590de80ee0d3b5e25636fa8" ns2:_="" ns3:_="">
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="634edf18-62ba-46f2-a3a7-063d8fb172d8">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="c44aea68-f73b-45d5-b042-7c498dcb23dc" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010023058B3D7F88F54B8F614B4819A3D2C3" ma:contentTypeVersion="20" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="6e532cb5723e67282d1dbbae94493ff1">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="c44aea68-f73b-45d5-b042-7c498dcb23dc" xmlns:ns3="634edf18-62ba-46f2-a3a7-063d8fb172d8" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="6d34ce002620c796e605c4c6381de2f5" ns2:_="" ns3:_="">
     <xsd:import namespace="c44aea68-f73b-45d5-b042-7c498dcb23dc"/>
     <xsd:import namespace="634edf18-62ba-46f2-a3a7-063d8fb172d8"/>
     <xsd:element name="properties">
@@ -1234,7 +1251,7 @@
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="c44aea68-f73b-45d5-b042-7c498dcb23dc" elementFormDefault="qualified">
     <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="SharedWithUsers" ma:index="8" nillable="true" ma:displayName="Partagé avec" ma:internalName="SharedWithUsers" ma:readOnly="true">
+    <xsd:element name="SharedWithUsers" ma:index="8" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
       <xsd:complexType>
         <xsd:complexContent>
           <xsd:extension base="dms:UserMulti">
@@ -1253,7 +1270,7 @@
         </xsd:complexContent>
       </xsd:complexType>
     </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="9" nillable="true" ma:displayName="Partagé avec détails" ma:internalName="SharedWithDetails" ma:readOnly="true">
+    <xsd:element name="SharedWithDetails" ma:index="9" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Note">
           <xsd:maxLength value="255"/>
@@ -1302,7 +1319,7 @@
         <xsd:restriction base="dms:Text"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="17" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Balises d’images" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="2baaf764-73f0-4b4c-b8e1-b7d465e0804e" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="17" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="2baaf764-73f0-4b4c-b8e1-b7d465e0804e" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
       <xsd:complexType>
         <xsd:sequence>
           <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
@@ -1349,8 +1366,8 @@
         <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Type de contenu"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Titre"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
         <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
         <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
@@ -1439,34 +1456,25 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="634edf18-62ba-46f2-a3a7-063d8fb172d8">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="c44aea68-f73b-45d5-b042-7c498dcb23dc" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C80CA55F-9C30-47F6-AD5B-4C6F2F434811}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{06A74E17-7508-4913-AA55-9BE401C466DD}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="634edf18-62ba-46f2-a3a7-063d8fb172d8"/>
+    <ds:schemaRef ds:uri="c44aea68-f73b-45d5-b042-7c498dcb23dc"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6C9FB99-B02C-4D07-B771-27E0000684A7}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6C9FB99-B02C-4D07-B771-27E0000684A7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{06A74E17-7508-4913-AA55-9BE401C466DD}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2756C475-5299-4C09-BC2B-B90B2E8912D5}"/>
 </file>
--- a/data/NCC_Compiled_Tenure_Data_Sources/Blue Carbon - ATL Tenure Data.xlsx
+++ b/data/NCC_Compiled_Tenure_Data_Sources/Blue Carbon - ATL Tenure Data.xlsx
@@ -1216,8 +1216,8 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010023058B3D7F88F54B8F614B4819A3D2C3" ma:contentTypeVersion="20" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="6e532cb5723e67282d1dbbae94493ff1">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="c44aea68-f73b-45d5-b042-7c498dcb23dc" xmlns:ns3="634edf18-62ba-46f2-a3a7-063d8fb172d8" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="6d34ce002620c796e605c4c6381de2f5" ns2:_="" ns3:_="">
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010023058B3D7F88F54B8F614B4819A3D2C3" ma:contentTypeVersion="20" ma:contentTypeDescription="Crée un document." ma:contentTypeScope="" ma:versionID="9c95790c7176aca22ec34ce72732b57f">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="c44aea68-f73b-45d5-b042-7c498dcb23dc" xmlns:ns3="634edf18-62ba-46f2-a3a7-063d8fb172d8" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="25574f8a6590de80ee0d3b5e25636fa8" ns2:_="" ns3:_="">
     <xsd:import namespace="c44aea68-f73b-45d5-b042-7c498dcb23dc"/>
     <xsd:import namespace="634edf18-62ba-46f2-a3a7-063d8fb172d8"/>
     <xsd:element name="properties">
@@ -1251,7 +1251,7 @@
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="c44aea68-f73b-45d5-b042-7c498dcb23dc" elementFormDefault="qualified">
     <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="SharedWithUsers" ma:index="8" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
+    <xsd:element name="SharedWithUsers" ma:index="8" nillable="true" ma:displayName="Partagé avec" ma:internalName="SharedWithUsers" ma:readOnly="true">
       <xsd:complexType>
         <xsd:complexContent>
           <xsd:extension base="dms:UserMulti">
@@ -1270,7 +1270,7 @@
         </xsd:complexContent>
       </xsd:complexType>
     </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="9" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
+    <xsd:element name="SharedWithDetails" ma:index="9" nillable="true" ma:displayName="Partagé avec détails" ma:internalName="SharedWithDetails" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Note">
           <xsd:maxLength value="255"/>
@@ -1319,7 +1319,7 @@
         <xsd:restriction base="dms:Text"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="17" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="2baaf764-73f0-4b4c-b8e1-b7d465e0804e" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="17" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Balises d’images" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="2baaf764-73f0-4b4c-b8e1-b7d465e0804e" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
       <xsd:complexType>
         <xsd:sequence>
           <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
@@ -1366,8 +1366,8 @@
         <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Type de contenu"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Titre"/>
         <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
         <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
@@ -1476,5 +1476,5 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2756C475-5299-4C09-BC2B-B90B2E8912D5}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F43A0BA5-AA28-4826-BA86-088112381C82}"/>
 </file>